--- a/assets/data/熊野古道.xlsx
+++ b/assets/data/熊野古道.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vito\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VitoShaoGithub\Documents\Vitoshao\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C496CA93-0AAC-45A7-A7A4-4E38A1954EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198EAB17-2E34-4D41-9787-B296885F01C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1968CBBD-A421-4C5B-A8E8-95F8E75DDA5A}"/>
+    <workbookView xWindow="984" yWindow="828" windowWidth="18060" windowHeight="11148" xr2:uid="{1968CBBD-A421-4C5B-A8E8-95F8E75DDA5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 " sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="蒲島飯店" localSheetId="0">'Sheet1 '!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentManualCount="12"/>
+  <calcPr calcId="181029" concurrentManualCount="12"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -153,9 +153,6 @@
     <t>40. 石堂茶屋跡</t>
   </si>
   <si>
-    <t>39. 小和瀨渡丨場跡</t>
-  </si>
-  <si>
     <t>38.小口(大雲登山口)</t>
   </si>
   <si>
@@ -279,37 +276,43 @@
     <t>山水館川湯松屋酒店</t>
   </si>
   <si>
+    <t>繼櫻王子--&gt;湯峰王子--&gt;川湯</t>
+  </si>
+  <si>
+    <t>29. 小狗子峠</t>
+  </si>
+  <si>
+    <t>28. 高野坂</t>
+  </si>
+  <si>
+    <t>Guest House Kiyohime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morinonaka Guest House </t>
+  </si>
+  <si>
+    <t>新宮-Hanare</t>
+  </si>
+  <si>
+    <t>花之禦宿旅館</t>
+  </si>
+  <si>
+    <t>和歌山康福特茵酒店</t>
+  </si>
+  <si>
+    <t>浦島酒店</t>
+  </si>
+  <si>
+    <t>39. 小和瀨渡し場跡</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>紀伊田邊9:05 (公車) --&gt; 清姬之墓</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>清姬之墓--&gt;潼尻王子--&gt;近露 --&gt;繼櫻王子</t>
-  </si>
-  <si>
-    <t>繼櫻王子--&gt;湯峰王子--&gt;川湯</t>
-  </si>
-  <si>
-    <t>紀伊田邊9:05 (公車) --&gt; 清姬之墓</t>
-  </si>
-  <si>
-    <t>29. 小狗子峠</t>
-  </si>
-  <si>
-    <t>28. 高野坂</t>
-  </si>
-  <si>
-    <t>Guest House Kiyohime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morinonaka Guest House </t>
-  </si>
-  <si>
-    <t>新宮-Hanare</t>
-  </si>
-  <si>
-    <t>花之禦宿旅館</t>
-  </si>
-  <si>
-    <t>和歌山康福特茵酒店</t>
-  </si>
-  <si>
-    <t>浦島酒店</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -381,7 +384,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -415,39 +418,114 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -765,24 +843,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F41B419C-078E-4684-B4F5-ECF691C8B5BE}">
   <dimension ref="A1:K46"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.125" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="5.375" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="10.125" customWidth="1"/>
+    <col min="6" max="6" width="8.875" customWidth="1"/>
     <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="46.85546875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" style="14" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="46.875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="10" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
@@ -800,68 +878,68 @@
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="12" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="14">
+        <v>45379</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="10">
+        <v>20051</v>
+      </c>
+      <c r="K2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="10">
-        <v>45379</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="14">
-        <v>20051</v>
-      </c>
-      <c r="K2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="21">
         <v>45380</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="10"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -872,49 +950,49 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+    <row r="5" spans="1:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="21">
         <v>45381</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
+      <c r="D6" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="10"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="2"/>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -929,12 +1007,12 @@
       </c>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="10"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="7"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -944,12 +1022,12 @@
       </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
         <v>18</v>
@@ -959,12 +1037,12 @@
       </c>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="10"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
         <v>19</v>
@@ -974,12 +1052,12 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="10"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="7"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
         <v>20</v>
@@ -989,12 +1067,12 @@
       </c>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="10"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
         <v>21</v>
@@ -1004,47 +1082,47 @@
       </c>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
+    <row r="13" spans="1:11" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="12">
         <v>45382</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
+      <c r="E14" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="10"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1055,9 +1133,9 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="10"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1068,9 +1146,9 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="10"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1081,9 +1159,9 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="10"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1094,9 +1172,9 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="10"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1107,12 +1185,12 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="10"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
         <v>31</v>
@@ -1120,12 +1198,12 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="10"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="4"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
         <v>32</v>
@@ -1133,12 +1211,12 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="10"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="7"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
         <v>33</v>
@@ -1146,12 +1224,12 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="10"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="7"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
         <v>34</v>
@@ -1159,54 +1237,54 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="10"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="7"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
+    <row r="25" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="12">
         <v>45383</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="G26" s="1" t="s">
+      <c r="D26" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="G26" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="10"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1217,308 +1295,309 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="10"/>
+      <c r="B28" s="6"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="13"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="12">
+        <v>45384</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="10">
-        <v>45384</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="10"/>
+      <c r="B31" s="6"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="10"/>
+      <c r="B32" s="6"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="5"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="10"/>
+      <c r="B33" s="6"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="7"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="10"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="7"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H34" s="8"/>
+        <v>51</v>
+      </c>
+      <c r="H34" s="5"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="10"/>
+      <c r="B35" s="6"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="7"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="10"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="7"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H36" s="1"/>
-      <c r="I36" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I36" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="10"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="7"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="B39" s="12">
+        <v>45385</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="10">
-        <v>45385</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E39" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="10"/>
+      <c r="B40" s="6"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="7"/>
+      <c r="E40" s="4"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H40" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="H40" s="4"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="10"/>
+      <c r="B41" s="6"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="10">
+    <row r="42" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="21">
         <v>45386</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D43" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="10"/>
+      <c r="B44" s="6"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44" s="1"/>
+      <c r="F44" s="28"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+    <row r="45" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+    </row>
+    <row r="46" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="30">
+        <v>45387</v>
+      </c>
+      <c r="C46" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="10">
-        <v>45387</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
